--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89235</v>
+        <v>89237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89237</v>
+        <v>89239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1737-2022 artfynd.xlsx
+++ b/artfynd/S 1737-2022 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>88675994</v>
       </c>
       <c r="B4" t="n">
-        <v>89239</v>
+        <v>89241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
